--- a/workshop_prep/bob_item6_growth_innovation_backup.xlsx
+++ b/workshop_prep/bob_item6_growth_innovation_backup.xlsx
@@ -21,6 +21,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Accessories - New-Test Launches" sheetId="12" state="visible" r:id="rId12"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hardware-Packs Layers" sheetId="13" state="visible" r:id="rId13"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hardware-Packs New-Test" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="YTD2026 Footwear" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="YTD2026 Bow Windstopper Summary" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="YTD2026 Bow Windstopper Detail" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="YTD2026 HAYL Korea" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2628,6 +2632,4207 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Layer</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>FY2025_Sales</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>FY2025_Units</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>YTD2026_Sales</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>YTD2026_Units</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>YTD_units_pct_of_FY25</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Hiking shoes</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>30211532.94431267</v>
+      </c>
+      <c r="C2" t="n">
+        <v>39748</v>
+      </c>
+      <c r="D2" t="n">
+        <v>20903888.04738686</v>
+      </c>
+      <c r="E2" t="n">
+        <v>26238</v>
+      </c>
+      <c r="F2" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Trail running shoes</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1366306.16327984</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1951</v>
+      </c>
+      <c r="D3" t="n">
+        <v>546855.3407581999</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1120</v>
+      </c>
+      <c r="F3" t="n">
+        <v>57.4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Casual shoes</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1119038.07200056</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1352</v>
+      </c>
+      <c r="D4" t="n">
+        <v>91291.1724562</v>
+      </c>
+      <c r="E4" t="n">
+        <v>169</v>
+      </c>
+      <c r="F4" t="n">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Trekking shoes</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>12534967.23589773</v>
+      </c>
+      <c r="C5" t="n">
+        <v>15553</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2435555.63321816</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2756</v>
+      </c>
+      <c r="F5" t="n">
+        <v>17.7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Ordertype Group</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Units</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Closeoutorder Group</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>129347.53</v>
+      </c>
+      <c r="C2" t="n">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Preorder Group</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>-406467.5500000001</v>
+      </c>
+      <c r="C3" t="n">
+        <v>-3464</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Reorder Group</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>107049.7669952</v>
+      </c>
+      <c r="C4" t="n">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>43987.2585497</v>
+      </c>
+      <c r="C5" t="n">
+        <v>94</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:U48"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Sales Channel</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Sales Market</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Customer Group</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Layer</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Ordertype Group</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Garp SEK Sales</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Budget</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Units Sold</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>UPT</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>ATV</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Visitors</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Transactions (All)</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Transactions net</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>Garp SEK Margin</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>Garp SEK Margin %</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>Garp SEK COGS</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>Other COGS Garp SEK</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>E-com</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>HAGLÖFS EXTERNAL E-COM AT</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Accessories</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Bow Windstopper Glove</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Reorder Group</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>701.4400000000001</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L2" t="n">
+        <v>740.0422013116623</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P2" t="n">
+        <v>556.6400000000001</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.7935675182481753</v>
+      </c>
+      <c r="R2" t="n">
+        <v>144.8</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>Bow Windstopper Glove</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Unisex</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>E-com</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>HAGLÖFS EXTERNAL E-COM AT</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Accessories</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Bow Windstopper II Glove</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Reorder Group</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>511.87</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L3" t="n">
+        <v>532.7979182295574</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1</v>
+      </c>
+      <c r="P3" t="n">
+        <v>373.3</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.7292867329595405</v>
+      </c>
+      <c r="R3" t="n">
+        <v>138.57</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Bow Windstopper Glove</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Unisex</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>E-com</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Denmark</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>HAGLÖFS EXTERNAL E-COM DK</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Accessories</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Bow Windstopper Glove</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Reorder Group</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>1334.4</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>2</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L4" t="n">
+        <v>287.9999999999999</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>5</v>
+      </c>
+      <c r="O4" t="n">
+        <v>5</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1045.22</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.7832883693045565</v>
+      </c>
+      <c r="R4" t="n">
+        <v>289.1799999999999</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Bow Windstopper Glove</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Unisex</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>E-com</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Denmark</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>HAGLÖFS EXTERNAL E-COM DK</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Accessories</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Bow Windstopper II Glove</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Reorder Group</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>2719.12</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>5</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" t="n">
+        <v>576.0033959285661</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>5</v>
+      </c>
+      <c r="O5" t="n">
+        <v>5</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2026.97</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.7454507340610197</v>
+      </c>
+      <c r="R5" t="n">
+        <v>692.1500000000001</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Bow Windstopper Glove</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Unisex</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>E-com</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Denmark</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Personnel Purchase</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Accessories</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Bow Windstopper Glove</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Reorder Group</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>282.08</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" t="n">
+        <v>300.2980837473385</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P6" t="n">
+        <v>137.28</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.4866704480998298</v>
+      </c>
+      <c r="R6" t="n">
+        <v>144.8</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Bow Windstopper Glove</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Unisex</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>E-com</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>HAGLÖFS EXTERNAL E-COM FI</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Accessories</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Bow Windstopper II Glove</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Reorder Group</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>565.02</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>565.3255813953489</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1</v>
+      </c>
+      <c r="P7" t="n">
+        <v>426.59</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.7549998230151145</v>
+      </c>
+      <c r="R7" t="n">
+        <v>138.43</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Bow Windstopper Glove</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Unisex</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>E-com</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>HAGLÖFS EXTERNAL E-COM FR</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Accessories</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Bow Windstopper II Glove</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Reorder Group</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>1070.63</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L8" t="n">
+        <v>140.5938348885536</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>8</v>
+      </c>
+      <c r="O8" t="n">
+        <v>8</v>
+      </c>
+      <c r="P8" t="n">
+        <v>793.7699999999999</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.7414045935570645</v>
+      </c>
+      <c r="R8" t="n">
+        <v>276.86</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Bow Windstopper Glove</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Unisex</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>E-com</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>HAGLÖFS EXTERNAL E-COM DE</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Accessories</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Bow Windstopper Glove</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Reorder Group</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>2109.07</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" t="n">
+        <v>721.3495100757996</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>3</v>
+      </c>
+      <c r="O9" t="n">
+        <v>3</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1675.09</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.7942315807441194</v>
+      </c>
+      <c r="R9" t="n">
+        <v>433.98</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Bow Windstopper Glove</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Unisex</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>E-com</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>HAGLÖFS EXTERNAL E-COM DE</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Accessories</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Bow Windstopper II Glove</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Reorder Group</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>6427.51</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>11</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.3666666666666666</v>
+      </c>
+      <c r="L10" t="n">
+        <v>218.8847235409611</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>30</v>
+      </c>
+      <c r="O10" t="n">
+        <v>30</v>
+      </c>
+      <c r="P10" t="n">
+        <v>4627.880000000001</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.7200113263145449</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1799.63</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Bow Windstopper Glove</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Unisex</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>E-com</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>HAGLÖFS EXTERNAL E-COM IT</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Accessories</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Bow Windstopper II Glove</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Reorder Group</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>2270.04</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>4</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1164.607321131448</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2</v>
+      </c>
+      <c r="O11" t="n">
+        <v>2</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1716.32</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.7560747828232102</v>
+      </c>
+      <c r="R11" t="n">
+        <v>553.72</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Bow Windstopper Glove</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Unisex</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>E-com</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>HAGLÖFS EXTERNAL E-COM NL</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Accessories</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Bow Windstopper Glove</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Reorder Group</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>1440.63</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" t="n">
+        <v>733.9357913808192</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>2</v>
+      </c>
+      <c r="O12" t="n">
+        <v>2</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1151.03</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.7989768365229102</v>
+      </c>
+      <c r="R12" t="n">
+        <v>289.6</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Bow Windstopper Glove</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Unisex</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>E-com</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>HAGLÖFS EXTERNAL E-COM NL</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Accessories</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Bow Windstopper II Glove</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Reorder Group</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>1826.72</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="L13" t="n">
+        <v>212.0104065627656</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>9</v>
+      </c>
+      <c r="O13" t="n">
+        <v>9</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1411.43</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.7726580975737934</v>
+      </c>
+      <c r="R13" t="n">
+        <v>415.29</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Bow Windstopper Glove</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Unisex</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>E-com</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>HAGLÖFS EXTERNAL E-COM NO</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Accessories</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Bow Windstopper II Glove</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Reorder Group</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>2433.506995199999</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>5</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="L14" t="n">
+        <v>350.9028571428572</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>7</v>
+      </c>
+      <c r="O14" t="n">
+        <v>7</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1741.3569952</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.7155750933261176</v>
+      </c>
+      <c r="R14" t="n">
+        <v>692.1500000000001</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Bow Windstopper Glove</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Unisex</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>E-com</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>HAGLÖFS EXTERNAL E-COM ES</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Accessories</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Bow Windstopper Glove</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Reorder Group</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>695.65</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" t="n">
+        <v>733.9335614485315</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>1</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1</v>
+      </c>
+      <c r="P15" t="n">
+        <v>550.8499999999999</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.7918493495292172</v>
+      </c>
+      <c r="R15" t="n">
+        <v>144.8</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Bow Windstopper Glove</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Unisex</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>E-com</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>HAGLÖFS EXTERNAL E-COM ES</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Accessories</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Bow Windstopper II Glove</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Reorder Group</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>4249.139999999999</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>7</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.6363636363636364</v>
+      </c>
+      <c r="L16" t="n">
+        <v>400.2968175658063</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>11</v>
+      </c>
+      <c r="O16" t="n">
+        <v>11</v>
+      </c>
+      <c r="P16" t="n">
+        <v>3280.13</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.7719515007742743</v>
+      </c>
+      <c r="R16" t="n">
+        <v>969.01</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Bow Windstopper Glove</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Unisex</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>E-com</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>HAGLÖFS EXTERNAL E-COM SE</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Accessories</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Bow Windstopper Glove</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Reorder Group</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>7168</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>13</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1.181818181818182</v>
+      </c>
+      <c r="L17" t="n">
+        <v>651.6363636363636</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>11</v>
+      </c>
+      <c r="O17" t="n">
+        <v>11</v>
+      </c>
+      <c r="P17" t="n">
+        <v>5284.309999999999</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.7372084263392856</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1883.69</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Bow Windstopper Glove</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Unisex</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>E-com</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>HAGLÖFS EXTERNAL E-COM SE</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Accessories</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Bow Windstopper II Glove</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Reorder Group</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>15840</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>32</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0.6956521739130435</v>
+      </c>
+      <c r="L18" t="n">
+        <v>344.3478260869565</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>46</v>
+      </c>
+      <c r="O18" t="n">
+        <v>46</v>
+      </c>
+      <c r="P18" t="n">
+        <v>11409.76</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.7203131313131312</v>
+      </c>
+      <c r="R18" t="n">
+        <v>4430.240000000001</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Bow Windstopper Glove</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Unisex</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>E-com</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>HAGLÖFS EXTERNAL E-COM UK</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Accessories</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Bow Windstopper II Glove</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Reorder Group</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>7753.52</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>14</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0.4666666666666667</v>
+      </c>
+      <c r="L19" t="n">
+        <v>274.0178770855342</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>30</v>
+      </c>
+      <c r="O19" t="n">
+        <v>30</v>
+      </c>
+      <c r="P19" t="n">
+        <v>5815.189999999999</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.7500064486839525</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1938.33</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Bow Windstopper Glove</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Unisex</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>HAGLÖFS BRAND STORE HELSINKI</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Accessories</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Bow Windstopper II Glove</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Reorder Group</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1107.44</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Bow Windstopper Glove</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Unisex</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>HELSINKI OUTLET VILLAGE</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Accessories</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Bow Windstopper II Glove</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Reorder Group</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>4153.35</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Bow Windstopper Glove</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Unisex</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>*BLANK*</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Accessories</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Bow Windstopper Glove</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>2857.84503175</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>7</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1</v>
+      </c>
+      <c r="L22" t="n">
+        <v>423.2747142857144</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>7</v>
+      </c>
+      <c r="O22" t="n">
+        <v>7</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1718.32117175</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0.6012646426450168</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1139.52386</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Bow Windstopper Glove</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Unisex</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>*BLANK*</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Accessories</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Bow Windstopper II Glove</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>8030.70590855</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
+        <v>15</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1</v>
+      </c>
+      <c r="L23" t="n">
+        <v>556.0508000000001</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>15</v>
+      </c>
+      <c r="O23" t="n">
+        <v>15</v>
+      </c>
+      <c r="P23" t="n">
+        <v>5591.522692550001</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0.6962678942827317</v>
+      </c>
+      <c r="R23" t="n">
+        <v>2439.183215999999</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Bow Windstopper Glove</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Unisex</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>*BLANK*</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Accessories</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Bow Windstopper II Glove</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>4637.907609399999</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>10</v>
+      </c>
+      <c r="K24" t="n">
+        <v>1.111111111111111</v>
+      </c>
+      <c r="L24" t="n">
+        <v>534.4650000000001</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>9</v>
+      </c>
+      <c r="O24" t="n">
+        <v>9</v>
+      </c>
+      <c r="P24" t="n">
+        <v>3279.761314599999</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0.7071640038608484</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1358.1462948</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Bow Windstopper Glove</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Unisex</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>*BLANK*</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Accessories</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Bow Windstopper Glove</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>15900.8</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>36</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="L25" t="n">
+        <v>397.52</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>40</v>
+      </c>
+      <c r="O25" t="n">
+        <v>40</v>
+      </c>
+      <c r="P25" t="n">
+        <v>10700.8</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0.6729724290601732</v>
+      </c>
+      <c r="R25" t="n">
+        <v>5199.999999999999</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Bow Windstopper Glove</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Unisex</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>*BLANK*</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Accessories</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Bow Windstopper II Glove</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>12560</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>26</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0.9285714285714286</v>
+      </c>
+      <c r="L26" t="n">
+        <v>448.5714285714286</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>28</v>
+      </c>
+      <c r="O26" t="n">
+        <v>28</v>
+      </c>
+      <c r="P26" t="n">
+        <v>8960.74</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0.7134347133757961</v>
+      </c>
+      <c r="R26" t="n">
+        <v>3599.26</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Bow Windstopper Glove</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Unisex</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Wholesale</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Benelux</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>BENEFITT</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Accessories</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Bow Windstopper II Glove</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Reorder Group</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>400.85</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1</v>
+      </c>
+      <c r="K27" t="n">
+        <v>1</v>
+      </c>
+      <c r="L27" t="n">
+        <v>422.9098944967208</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>1</v>
+      </c>
+      <c r="O27" t="n">
+        <v>1</v>
+      </c>
+      <c r="P27" t="n">
+        <v>262.01</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0.6536360234501684</v>
+      </c>
+      <c r="R27" t="n">
+        <v>138.84</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Bow Windstopper Glove</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Unisex</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Wholesale</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Benelux</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>HAGLÖFS EXTERNAL SWEDEN</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Accessories</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Bow Windstopper Glove</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Reorder Group</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>413.61</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1</v>
+      </c>
+      <c r="K28" t="n">
+        <v>1</v>
+      </c>
+      <c r="L28" t="n">
+        <v>422.9063190862196</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>1</v>
+      </c>
+      <c r="O28" t="n">
+        <v>1</v>
+      </c>
+      <c r="P28" t="n">
+        <v>267.85</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0.6475907255627282</v>
+      </c>
+      <c r="R28" t="n">
+        <v>145.76</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Bow Windstopper Glove</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Unisex</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Wholesale</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Denmark</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>*MISSING*</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Accessories</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Bow Windstopper II Glove</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Reorder Group</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
+        <v>1038.28</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>3</v>
+      </c>
+      <c r="K29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L29" t="n">
+        <v>546.9750160823377</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>2</v>
+      </c>
+      <c r="O29" t="n">
+        <v>2</v>
+      </c>
+      <c r="P29" t="n">
+        <v>622.99</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0.600021188889317</v>
+      </c>
+      <c r="R29" t="n">
+        <v>415.29</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Bow Windstopper Glove</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Unisex</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Wholesale</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Denmark</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>ILLUM/LOGISTIKKOMPAGNIET</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Accessories</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Bow Windstopper II Glove</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Preorder Group</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>-324.5</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="L30" t="n">
+        <v>-332.4795081967213</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>1</v>
+      </c>
+      <c r="O30" t="n">
+        <v>1</v>
+      </c>
+      <c r="P30" t="n">
+        <v>-185.84</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0.5726964560862866</v>
+      </c>
+      <c r="R30" t="n">
+        <v>-138.66</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Bow Windstopper Glove</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Unisex</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Wholesale</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Export Other</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>*MISSING*</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Accessories</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Bow Windstopper Glove</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Preorder Group</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
+        <v>-418790.21</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>-3513</v>
+      </c>
+      <c r="K31" t="n">
+        <v>-1756.5</v>
+      </c>
+      <c r="L31" t="n">
+        <v>-223974.8267339816</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>2</v>
+      </c>
+      <c r="O31" t="n">
+        <v>2</v>
+      </c>
+      <c r="P31" t="n">
+        <v>81726.22000000003</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>-0.1951483536351053</v>
+      </c>
+      <c r="R31" t="n">
+        <v>-500516.4300000001</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Bow Windstopper Glove</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Unisex</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Wholesale</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>INTERSPORT</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Accessories</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Bow Windstopper Glove</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Reorder Group</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
+        <v>-380.93</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K32" t="n">
+        <v>-1</v>
+      </c>
+      <c r="L32" t="n">
+        <v>-386.3952298272869</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
+        <v>1</v>
+      </c>
+      <c r="O32" t="n">
+        <v>1</v>
+      </c>
+      <c r="P32" t="n">
+        <v>-380.93</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>1</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Bow Windstopper Glove</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Unisex</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Wholesale</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>INTERSPORT</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Accessories</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Bow Windstopper II Glove</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Reorder Group</t>
+        </is>
+      </c>
+      <c r="H33" t="n">
+        <v>36658.94000000001</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="n">
+        <v>150</v>
+      </c>
+      <c r="K33" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="L33" t="n">
+        <v>4745.244869661674</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>8</v>
+      </c>
+      <c r="O33" t="n">
+        <v>8</v>
+      </c>
+      <c r="P33" t="n">
+        <v>15889.24</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0.4334342455073714</v>
+      </c>
+      <c r="R33" t="n">
+        <v>20769.7</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Bow Windstopper Glove</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Unisex</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Wholesale</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>INTERSPORT</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Accessories</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Bow Windstopper II Glove</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Closeoutorder Group</t>
+        </is>
+      </c>
+      <c r="H34" t="n">
+        <v>37244.2</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="n">
+        <v>151</v>
+      </c>
+      <c r="K34" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="L34" t="n">
+        <v>19107.53466444814</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
+        <v>2</v>
+      </c>
+      <c r="O34" t="n">
+        <v>2</v>
+      </c>
+      <c r="P34" t="n">
+        <v>16341.27</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0.4387601290939261</v>
+      </c>
+      <c r="R34" t="n">
+        <v>20902.93</v>
+      </c>
+      <c r="S34" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Bow Windstopper Glove</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Unisex</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Wholesale</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>MAANPUOLUSTUSKORKEAKOULU /86</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Accessories</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Bow Windstopper II Glove</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Reorder Group</t>
+        </is>
+      </c>
+      <c r="H35" t="n">
+        <v>384.97</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="n">
+        <v>1</v>
+      </c>
+      <c r="K35" t="n">
+        <v>1</v>
+      </c>
+      <c r="L35" t="n">
+        <v>400.7095836459115</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
+        <v>1</v>
+      </c>
+      <c r="O35" t="n">
+        <v>1</v>
+      </c>
+      <c r="P35" t="n">
+        <v>246.13</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0.6393485206639479</v>
+      </c>
+      <c r="R35" t="n">
+        <v>138.84</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Bow Windstopper Glove</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Unisex</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Wholesale</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>PARTIOAITTA</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Accessories</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Bow Windstopper Glove</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Reorder Group</t>
+        </is>
+      </c>
+      <c r="H36" t="n">
+        <v>-761.97</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="n">
+        <v>-2</v>
+      </c>
+      <c r="K36" t="n">
+        <v>-1</v>
+      </c>
+      <c r="L36" t="n">
+        <v>-386.4510189162021</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="n">
+        <v>2</v>
+      </c>
+      <c r="O36" t="n">
+        <v>2</v>
+      </c>
+      <c r="P36" t="n">
+        <v>-761.97</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>1</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Bow Windstopper Glove</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Unisex</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Wholesale</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>PARTIOAITTA</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Accessories</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Bow Windstopper II Glove</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Closeoutorder Group</t>
+        </is>
+      </c>
+      <c r="H37" t="n">
+        <v>76708.27</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="n">
+        <v>311</v>
+      </c>
+      <c r="K37" t="n">
+        <v>311</v>
+      </c>
+      <c r="L37" t="n">
+        <v>78707.87548530227</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" t="n">
+        <v>1</v>
+      </c>
+      <c r="O37" t="n">
+        <v>1</v>
+      </c>
+      <c r="P37" t="n">
+        <v>33656.54000000001</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0.4387602536206331</v>
+      </c>
+      <c r="R37" t="n">
+        <v>43051.73</v>
+      </c>
+      <c r="S37" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Bow Windstopper Glove</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Unisex</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Wholesale</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>SPORTIA</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Accessories</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Bow Windstopper II Glove</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Closeoutorder Group</t>
+        </is>
+      </c>
+      <c r="H38" t="n">
+        <v>5277.34</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="n">
+        <v>22</v>
+      </c>
+      <c r="K38" t="n">
+        <v>22</v>
+      </c>
+      <c r="L38" t="n">
+        <v>5567.766752209865</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="n">
+        <v>1</v>
+      </c>
+      <c r="O38" t="n">
+        <v>1</v>
+      </c>
+      <c r="P38" t="n">
+        <v>2229.45</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>0.4224571469717698</v>
+      </c>
+      <c r="R38" t="n">
+        <v>3047.89</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Bow Windstopper Glove</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Unisex</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Wholesale</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>URHEILU OY</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Accessories</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Bow Windstopper II Glove</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Closeoutorder Group</t>
+        </is>
+      </c>
+      <c r="H39" t="n">
+        <v>10117.72</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="n">
+        <v>40</v>
+      </c>
+      <c r="K39" t="n">
+        <v>40</v>
+      </c>
+      <c r="L39" t="n">
+        <v>10123.19199567334</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" t="n">
+        <v>1</v>
+      </c>
+      <c r="O39" t="n">
+        <v>1</v>
+      </c>
+      <c r="P39" t="n">
+        <v>4576.009999999999</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>0.4522767975393666</v>
+      </c>
+      <c r="R39" t="n">
+        <v>5541.71</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Bow Windstopper Glove</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Unisex</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Wholesale</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>VELJEKSET KESKINEN OY</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Accessories</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Bow Windstopper II Glove</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Preorder Group</t>
+        </is>
+      </c>
+      <c r="H40" t="n">
+        <v>12647.16</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" t="n">
+        <v>50</v>
+      </c>
+      <c r="K40" t="n">
+        <v>50</v>
+      </c>
+      <c r="L40" t="n">
+        <v>12654</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" t="n">
+        <v>1</v>
+      </c>
+      <c r="O40" t="n">
+        <v>1</v>
+      </c>
+      <c r="P40" t="n">
+        <v>5720.24</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>0.4522944281562026</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6926.92</v>
+      </c>
+      <c r="S40" t="n">
+        <v>0</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Bow Windstopper Glove</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Unisex</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Wholesale</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>HARDLOOP</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Accessories</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Bow Windstopper II Glove</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Reorder Group</t>
+        </is>
+      </c>
+      <c r="H41" t="n">
+        <v>395.72</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" t="n">
+        <v>1</v>
+      </c>
+      <c r="K41" t="n">
+        <v>1</v>
+      </c>
+      <c r="L41" t="n">
+        <v>406.0354963948974</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" t="n">
+        <v>1</v>
+      </c>
+      <c r="O41" t="n">
+        <v>1</v>
+      </c>
+      <c r="P41" t="n">
+        <v>257.29</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>0.6501819468310926</v>
+      </c>
+      <c r="R41" t="n">
+        <v>138.43</v>
+      </c>
+      <c r="S41" t="n">
+        <v>0</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Bow Windstopper Glove</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Unisex</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Wholesale</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>MEGA SPORT S.A</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Accessories</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Bow Windstopper II Glove</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Reorder Group</t>
+        </is>
+      </c>
+      <c r="H42" t="n">
+        <v>547.4</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" t="n">
+        <v>2</v>
+      </c>
+      <c r="K42" t="n">
+        <v>2</v>
+      </c>
+      <c r="L42" t="n">
+        <v>561.6694398225179</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" t="n">
+        <v>1</v>
+      </c>
+      <c r="O42" t="n">
+        <v>1</v>
+      </c>
+      <c r="P42" t="n">
+        <v>270.54</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>0.4942272561198392</v>
+      </c>
+      <c r="R42" t="n">
+        <v>276.86</v>
+      </c>
+      <c r="S42" t="n">
+        <v>0</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Bow Windstopper Glove</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Unisex</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Wholesale</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>GEP COMMUNICATION GROUP AB</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Accessories</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Bow Windstopper Glove</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Reorder Group</t>
+        </is>
+      </c>
+      <c r="H43" t="n">
+        <v>762</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="n">
+        <v>2</v>
+      </c>
+      <c r="K43" t="n">
+        <v>2</v>
+      </c>
+      <c r="L43" t="n">
+        <v>762</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" t="n">
+        <v>1</v>
+      </c>
+      <c r="O43" t="n">
+        <v>1</v>
+      </c>
+      <c r="P43" t="n">
+        <v>470.48</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>0.6174278215223097</v>
+      </c>
+      <c r="R43" t="n">
+        <v>291.52</v>
+      </c>
+      <c r="S43" t="n">
+        <v>0</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Bow Windstopper Glove</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Unisex</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Wholesale</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>KLÄDPOOLEN I NORR AB</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Accessories</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Bow Windstopper II Glove</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Reorder Group</t>
+        </is>
+      </c>
+      <c r="H44" t="n">
+        <v>354.33</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" t="n">
+        <v>1</v>
+      </c>
+      <c r="K44" t="n">
+        <v>1</v>
+      </c>
+      <c r="L44" t="n">
+        <v>354.33</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" t="n">
+        <v>1</v>
+      </c>
+      <c r="O44" t="n">
+        <v>1</v>
+      </c>
+      <c r="P44" t="n">
+        <v>215.9</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>0.6093189964157706</v>
+      </c>
+      <c r="R44" t="n">
+        <v>138.43</v>
+      </c>
+      <c r="S44" t="n">
+        <v>0</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Bow Windstopper Glove</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Unisex</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Wholesale</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Personnel Purchase</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Accessories</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Bow Windstopper II Glove</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Reorder Group</t>
+        </is>
+      </c>
+      <c r="H45" t="n">
+        <v>266.7</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" t="n">
+        <v>1</v>
+      </c>
+      <c r="K45" t="n">
+        <v>1</v>
+      </c>
+      <c r="L45" t="n">
+        <v>266.7</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" t="n">
+        <v>1</v>
+      </c>
+      <c r="O45" t="n">
+        <v>1</v>
+      </c>
+      <c r="P45" t="n">
+        <v>128.27</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>0.4809523809523809</v>
+      </c>
+      <c r="R45" t="n">
+        <v>138.43</v>
+      </c>
+      <c r="S45" t="n">
+        <v>0</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Bow Windstopper Glove</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Unisex</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Wholesale</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>SGN</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Accessories</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Bow Windstopper II Glove</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Reorder Group</t>
+        </is>
+      </c>
+      <c r="H46" t="n">
+        <v>1714.25</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" t="n">
+        <v>5</v>
+      </c>
+      <c r="K46" t="n">
+        <v>5</v>
+      </c>
+      <c r="L46" t="n">
+        <v>1714.25</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" t="n">
+        <v>1</v>
+      </c>
+      <c r="O46" t="n">
+        <v>1</v>
+      </c>
+      <c r="P46" t="n">
+        <v>1021.49</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>0.5958815808662681</v>
+      </c>
+      <c r="R46" t="n">
+        <v>692.76</v>
+      </c>
+      <c r="S46" t="n">
+        <v>0</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Bow Windstopper Glove</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Unisex</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Wholesale</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>SWETT AB</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Accessories</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Bow Windstopper II Glove</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Reorder Group</t>
+        </is>
+      </c>
+      <c r="H47" t="n">
+        <v>-354.33</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K47" t="n">
+        <v>-1</v>
+      </c>
+      <c r="L47" t="n">
+        <v>-354.33</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" t="n">
+        <v>1</v>
+      </c>
+      <c r="O47" t="n">
+        <v>1</v>
+      </c>
+      <c r="P47" t="n">
+        <v>-354.33</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>1</v>
+      </c>
+      <c r="R47" t="n">
+        <v>0</v>
+      </c>
+      <c r="S47" t="n">
+        <v>0</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Bow Windstopper Glove</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Unisex</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Wholesale</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>TAYMOUTH CLUB LIMITED</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Accessories</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Bow Windstopper II Glove</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Reorder Group</t>
+        </is>
+      </c>
+      <c r="H48" t="n">
+        <v>6211.599999999999</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" t="n">
+        <v>15</v>
+      </c>
+      <c r="K48" t="n">
+        <v>15</v>
+      </c>
+      <c r="L48" t="n">
+        <v>6503.245550455021</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" t="n">
+        <v>1</v>
+      </c>
+      <c r="O48" t="n">
+        <v>1</v>
+      </c>
+      <c r="P48" t="n">
+        <v>4135.15</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>0.6657141477236139</v>
+      </c>
+      <c r="R48" t="n">
+        <v>2076.45</v>
+      </c>
+      <c r="S48" t="n">
+        <v>0</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Bow Windstopper Glove</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Unisex</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Period</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Sales_SEK</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Units</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Preorder_share_pct</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>FY2025 (full year)</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>6662038.96</v>
+      </c>
+      <c r="C2" t="n">
+        <v>16136</v>
+      </c>
+      <c r="D2" t="n">
+        <v>95.3</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>YTD2026</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>7898081.58</v>
+      </c>
+      <c r="C3" t="n">
+        <v>17385</v>
+      </c>
+      <c r="D3" t="n">
+        <v>100</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
